--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-pregnancy-observation.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-pregnancy-observation.header.langue</t>
+    <t>fr-lm-pregnancy-observation.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,13 +451,13 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-pregnancy-observation.directSubject[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-devicehttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professionalhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedure</t>
   </si>
   <si>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="201">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,10 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut de l'observation</t>
+  </si>
+  <si>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -970,7 +967,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="45.10546875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="56.1328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2627,7 +2624,7 @@
         <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2657,31 +2654,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2695,10 +2692,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2724,10 +2721,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2778,7 +2775,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2795,10 +2792,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2824,10 +2821,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2878,7 +2875,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2895,10 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2921,13 +2918,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>144</v>
-      </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2978,7 +2975,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2995,10 +2992,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3021,13 +3018,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>147</v>
-      </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3078,7 +3075,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3095,10 +3092,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3124,10 +3121,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3157,11 +3154,11 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Z22" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Z22" t="s" s="2">
-        <v>151</v>
-      </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
       </c>
@@ -3178,7 +3175,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3195,10 +3192,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3224,10 +3221,10 @@
         <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3257,11 +3254,11 @@
         <v>73</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="Z23" t="s" s="2">
-        <v>155</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>73</v>
       </c>
@@ -3278,7 +3275,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3295,10 +3292,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3324,10 +3321,10 @@
         <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3378,7 +3375,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3395,10 +3392,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3421,13 +3418,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>160</v>
-      </c>
       <c r="M25" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3478,7 +3475,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3495,10 +3492,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3524,10 +3521,10 @@
         <v>80</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3578,7 +3575,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3595,10 +3592,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3621,13 +3618,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="M27" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3678,7 +3675,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -3695,10 +3692,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3721,13 +3718,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="M28" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3778,7 +3775,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3795,10 +3792,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3824,10 +3821,10 @@
         <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3878,7 +3875,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3895,10 +3892,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3924,10 +3921,10 @@
         <v>80</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3978,7 +3975,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3995,10 +3992,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4021,13 +4018,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="L31" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="M31" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4078,7 +4075,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4095,10 +4092,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4121,13 +4118,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4178,7 +4175,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4195,10 +4192,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4224,10 +4221,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4278,7 +4275,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4295,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4324,10 +4321,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4378,7 +4375,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4395,10 +4392,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4424,10 +4421,10 @@
         <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4478,7 +4475,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4495,10 +4492,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4521,13 +4518,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L36" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="M36" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4578,7 +4575,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4595,10 +4592,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4621,13 +4618,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L37" t="s" s="2">
-        <v>189</v>
-      </c>
       <c r="M37" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4678,7 +4675,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4695,10 +4692,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4724,10 +4721,10 @@
         <v>131</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4778,7 +4775,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4795,10 +4792,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4821,13 +4818,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4878,7 +4875,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4895,10 +4892,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4924,10 +4921,10 @@
         <v>80</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4978,7 +4975,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -4995,10 +4992,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5021,13 +5018,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="L41" t="s" s="2">
-        <v>198</v>
-      </c>
       <c r="M41" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5078,7 +5075,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5095,10 +5092,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5121,13 +5118,13 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L42" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="M42" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5178,7 +5175,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
